--- a/modelos_x_cliente/BAYER CAMPO.xlsx
+++ b/modelos_x_cliente/BAYER CAMPO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Leonardo\Documents\LEONARDO\Gerador-de-fichas-de-EPI\modelos_x_cliente\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Leonardo GAP\Documents\Gerador-de-fichas-de-EPI\modelos_x_cliente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E02206-357D-4CCB-AC0D-2147F3C12B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7519FEB-7B98-4EA4-B8CC-06E7FC0A125D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="BAYER ENGENHARIA (OBRA)" sheetId="2" r:id="rId1"/>
     <sheet name="BAYER CAMPO " sheetId="5" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028" iterateDelta="1E-4"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="71">
   <si>
     <t>UNIFORMES E EPIs PARA COLABORADORES BAYER</t>
   </si>
@@ -1285,6 +1285,78 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1305,78 +1377,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1710,21 +1710,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:26" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="95" t="s">
+      <c r="B2" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
+      <c r="M2" s="80"/>
+      <c r="N2" s="80"/>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
@@ -1739,59 +1739,59 @@
     </row>
     <row r="3" spans="2:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:26" s="3" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="96" t="s">
+      <c r="B4" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="98" t="s">
+      <c r="C4" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="100" t="s">
+      <c r="D4" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="102" t="s">
+      <c r="E4" s="87" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="104" t="s">
+      <c r="F4" s="89" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="105"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="88" t="s">
+      <c r="G4" s="90"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="89"/>
-      <c r="K4" s="90"/>
-      <c r="L4" s="88" t="s">
+      <c r="J4" s="93"/>
+      <c r="K4" s="94"/>
+      <c r="L4" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="89"/>
-      <c r="N4" s="90"/>
-      <c r="O4" s="85" t="s">
+      <c r="M4" s="93"/>
+      <c r="N4" s="94"/>
+      <c r="O4" s="95" t="s">
         <v>8</v>
       </c>
-      <c r="P4" s="86"/>
-      <c r="Q4" s="87"/>
-      <c r="R4" s="88" t="s">
+      <c r="P4" s="96"/>
+      <c r="Q4" s="97"/>
+      <c r="R4" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="S4" s="89"/>
-      <c r="T4" s="90"/>
-      <c r="U4" s="91" t="s">
+      <c r="S4" s="93"/>
+      <c r="T4" s="94"/>
+      <c r="U4" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="89"/>
-      <c r="W4" s="90"/>
-      <c r="X4" s="91" t="s">
+      <c r="V4" s="93"/>
+      <c r="W4" s="94"/>
+      <c r="X4" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="Y4" s="89"/>
-      <c r="Z4" s="90"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="94"/>
     </row>
     <row r="5" spans="2:26" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="97"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="103"/>
+      <c r="B5" s="82"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="86"/>
+      <c r="E5" s="88"/>
       <c r="F5" s="11" t="s">
         <v>12</v>
       </c>
@@ -1855,7 +1855,7 @@
       </c>
     </row>
     <row r="6" spans="2:26" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="92">
+      <c r="B6" s="99">
         <v>3</v>
       </c>
       <c r="C6" s="41">
@@ -1890,7 +1890,7 @@
       <c r="Z6" s="19"/>
     </row>
     <row r="7" spans="2:26" ht="27" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="93"/>
+      <c r="B7" s="100"/>
       <c r="C7" s="48">
         <v>1</v>
       </c>
@@ -1927,7 +1927,7 @@
       <c r="Z7" s="7"/>
     </row>
     <row r="8" spans="2:26" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="93"/>
+      <c r="B8" s="100"/>
       <c r="C8" s="43">
         <v>1</v>
       </c>
@@ -1960,7 +1960,7 @@
       <c r="Z8" s="25"/>
     </row>
     <row r="9" spans="2:26" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="93"/>
+      <c r="B9" s="100"/>
       <c r="C9" s="43">
         <v>1</v>
       </c>
@@ -1993,7 +1993,7 @@
       <c r="Z9" s="25"/>
     </row>
     <row r="10" spans="2:26" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="93"/>
+      <c r="B10" s="100"/>
       <c r="C10" s="43">
         <v>2</v>
       </c>
@@ -2026,7 +2026,7 @@
       <c r="Z10" s="25"/>
     </row>
     <row r="11" spans="2:26" ht="24" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="93"/>
+      <c r="B11" s="100"/>
       <c r="C11" s="43"/>
       <c r="D11" s="44"/>
       <c r="E11" s="57" t="s">
@@ -2097,7 +2097,7 @@
       </c>
     </row>
     <row r="12" spans="2:26" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="93"/>
+      <c r="B12" s="100"/>
       <c r="C12" s="45">
         <v>1</v>
       </c>
@@ -2223,7 +2223,7 @@
       <c r="Z15" s="36"/>
     </row>
     <row r="16" spans="2:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="107" t="s">
+      <c r="B16" s="78" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="68">
@@ -2256,7 +2256,7 @@
       <c r="Z16" s="25"/>
     </row>
     <row r="17" spans="2:26" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="94"/>
+      <c r="B17" s="79"/>
       <c r="C17" s="71"/>
       <c r="D17" s="73"/>
       <c r="E17" s="60" t="s">
@@ -2285,7 +2285,7 @@
       <c r="Z17" s="7"/>
     </row>
     <row r="18" spans="2:26" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="94"/>
+      <c r="B18" s="79"/>
       <c r="C18" s="71"/>
       <c r="D18" s="73"/>
       <c r="E18" s="60" t="s">
@@ -2314,7 +2314,7 @@
       <c r="Z18" s="7"/>
     </row>
     <row r="19" spans="2:26" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="94"/>
+      <c r="B19" s="79"/>
       <c r="C19" s="71">
         <v>1</v>
       </c>
@@ -2345,7 +2345,7 @@
       <c r="Z19" s="7"/>
     </row>
     <row r="20" spans="2:26" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B20" s="94"/>
+      <c r="B20" s="79"/>
       <c r="C20" s="71">
         <v>1</v>
       </c>
@@ -2376,7 +2376,7 @@
       <c r="Z20" s="7"/>
     </row>
     <row r="21" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="94"/>
+      <c r="B21" s="79"/>
       <c r="C21" s="71">
         <v>1</v>
       </c>
@@ -2407,7 +2407,7 @@
       <c r="Z21" s="25"/>
     </row>
     <row r="22" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="94"/>
+      <c r="B22" s="79"/>
       <c r="C22" s="71">
         <v>1</v>
       </c>
@@ -2438,7 +2438,7 @@
       <c r="Z22" s="25"/>
     </row>
     <row r="23" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="94"/>
+      <c r="B23" s="79"/>
       <c r="C23" s="71">
         <v>1</v>
       </c>
@@ -2470,11 +2470,11 @@
     </row>
     <row r="24" spans="2:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="49"/>
-      <c r="C24" s="78" t="s">
+      <c r="C24" s="101" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="79"/>
-      <c r="E24" s="80"/>
+      <c r="D24" s="102"/>
+      <c r="E24" s="103"/>
       <c r="F24" s="38"/>
       <c r="G24" s="47" t="s">
         <v>53</v>
@@ -2486,11 +2486,11 @@
     </row>
     <row r="25" spans="2:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="49"/>
-      <c r="C25" s="78" t="s">
+      <c r="C25" s="101" t="s">
         <v>54</v>
       </c>
-      <c r="D25" s="79"/>
-      <c r="E25" s="80"/>
+      <c r="D25" s="102"/>
+      <c r="E25" s="103"/>
       <c r="F25" s="38"/>
       <c r="G25" s="47" t="s">
         <v>55</v>
@@ -2502,11 +2502,11 @@
     </row>
     <row r="26" spans="2:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="49"/>
-      <c r="C26" s="78" t="s">
+      <c r="C26" s="101" t="s">
         <v>56</v>
       </c>
-      <c r="D26" s="79"/>
-      <c r="E26" s="80"/>
+      <c r="D26" s="102"/>
+      <c r="E26" s="103"/>
       <c r="G26" s="47" t="s">
         <v>53</v>
       </c>
@@ -2517,10 +2517,10 @@
     </row>
     <row r="27" spans="2:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="49"/>
-      <c r="C27" s="81" t="s">
+      <c r="C27" s="104" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="81"/>
+      <c r="D27" s="104"/>
       <c r="E27" s="63" t="s">
         <v>58</v>
       </c>
@@ -2531,16 +2531,16 @@
       <c r="Z27" s="51"/>
     </row>
     <row r="28" spans="2:26" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="82" t="s">
+      <c r="B28" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="83"/>
-      <c r="D28" s="83"/>
-      <c r="E28" s="84" t="s">
+      <c r="C28" s="106"/>
+      <c r="D28" s="106"/>
+      <c r="E28" s="107" t="s">
         <v>60</v>
       </c>
-      <c r="F28" s="84"/>
-      <c r="G28" s="84"/>
+      <c r="F28" s="107"/>
+      <c r="G28" s="107"/>
       <c r="H28" s="39"/>
       <c r="I28" s="39"/>
       <c r="J28" s="39"/>
@@ -2604,7 +2604,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:Z36"/>
+  <dimension ref="B2:Z34"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.28515625" style="1" customWidth="1"/>
@@ -2629,21 +2629,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:26" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="95" t="s">
+      <c r="B2" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
+      <c r="M2" s="80"/>
+      <c r="N2" s="80"/>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
@@ -2658,59 +2658,59 @@
     </row>
     <row r="3" spans="2:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:26" s="3" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="96" t="s">
+      <c r="B4" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="98" t="s">
+      <c r="C4" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="100" t="s">
+      <c r="D4" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="102" t="s">
+      <c r="E4" s="87" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="104" t="s">
+      <c r="F4" s="89" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="105"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="88" t="s">
+      <c r="G4" s="90"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="89"/>
-      <c r="K4" s="90"/>
-      <c r="L4" s="88" t="s">
+      <c r="J4" s="93"/>
+      <c r="K4" s="94"/>
+      <c r="L4" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="89"/>
-      <c r="N4" s="90"/>
-      <c r="O4" s="85" t="s">
+      <c r="M4" s="93"/>
+      <c r="N4" s="94"/>
+      <c r="O4" s="95" t="s">
         <v>8</v>
       </c>
-      <c r="P4" s="86"/>
-      <c r="Q4" s="87"/>
-      <c r="R4" s="88" t="s">
+      <c r="P4" s="96"/>
+      <c r="Q4" s="97"/>
+      <c r="R4" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="S4" s="89"/>
-      <c r="T4" s="90"/>
-      <c r="U4" s="91" t="s">
+      <c r="S4" s="93"/>
+      <c r="T4" s="94"/>
+      <c r="U4" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="89"/>
-      <c r="W4" s="90"/>
-      <c r="X4" s="91" t="s">
+      <c r="V4" s="93"/>
+      <c r="W4" s="94"/>
+      <c r="X4" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="Y4" s="89"/>
-      <c r="Z4" s="90"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="94"/>
     </row>
     <row r="5" spans="2:26" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="97"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="103"/>
+      <c r="B5" s="82"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="86"/>
+      <c r="E5" s="88"/>
       <c r="F5" s="11" t="s">
         <v>12</v>
       </c>
@@ -2774,7 +2774,7 @@
       </c>
     </row>
     <row r="6" spans="2:26" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="92">
+      <c r="B6" s="99">
         <v>3</v>
       </c>
       <c r="C6" s="41">
@@ -2808,53 +2808,49 @@
       <c r="Y6" s="18"/>
       <c r="Z6" s="19"/>
     </row>
-    <row r="7" spans="2:26" ht="27" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="93"/>
-      <c r="C7" s="48">
+    <row r="7" spans="2:26" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="100"/>
+      <c r="C7" s="43">
         <v>1</v>
       </c>
       <c r="D7" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="56" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="33"/>
-      <c r="H7" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="23"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="22"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="24"/>
-      <c r="T7" s="25"/>
-      <c r="U7" s="23"/>
-      <c r="V7" s="24"/>
-      <c r="W7" s="25"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="4"/>
-      <c r="Z7" s="7"/>
+      <c r="E7" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" s="23"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="26"/>
+      <c r="P7" s="27"/>
+      <c r="Q7" s="28"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="23"/>
+      <c r="Y7" s="24"/>
+      <c r="Z7" s="25"/>
     </row>
     <row r="8" spans="2:26" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="93"/>
+      <c r="B8" s="100"/>
       <c r="C8" s="43">
         <v>1</v>
       </c>
       <c r="D8" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="77" t="s">
-        <v>61</v>
+      <c r="E8" s="46" t="s">
+        <v>32</v>
       </c>
       <c r="F8" s="23"/>
       <c r="G8" s="4"/>
@@ -2879,152 +2875,110 @@
       <c r="Z8" s="25"/>
     </row>
     <row r="9" spans="2:26" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="93"/>
+      <c r="B9" s="100"/>
       <c r="C9" s="43">
-        <v>1</v>
-      </c>
-      <c r="D9" s="42" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="46" t="s">
-        <v>32</v>
+        <v>2</v>
+      </c>
+      <c r="D9" s="44">
+        <v>44</v>
+      </c>
+      <c r="E9" s="57" t="s">
+        <v>67</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="4"/>
       <c r="H9" s="25"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="7"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="25"/>
       <c r="L9" s="23"/>
       <c r="M9" s="24"/>
       <c r="N9" s="25"/>
       <c r="O9" s="26"/>
       <c r="P9" s="27"/>
       <c r="Q9" s="28"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="6"/>
-      <c r="V9" s="4"/>
-      <c r="W9" s="7"/>
+      <c r="R9" s="23"/>
+      <c r="S9" s="24"/>
+      <c r="T9" s="25"/>
+      <c r="U9" s="23"/>
+      <c r="V9" s="24"/>
+      <c r="W9" s="25"/>
       <c r="X9" s="23"/>
       <c r="Y9" s="24"/>
       <c r="Z9" s="25"/>
     </row>
     <row r="10" spans="2:26" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="93"/>
-      <c r="C10" s="43">
-        <v>2</v>
-      </c>
-      <c r="D10" s="44">
-        <v>44</v>
-      </c>
-      <c r="E10" s="57" t="s">
-        <v>67</v>
-      </c>
-      <c r="F10" s="23"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="24"/>
-      <c r="N10" s="25"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="27"/>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="23"/>
-      <c r="S10" s="24"/>
-      <c r="T10" s="25"/>
-      <c r="U10" s="23"/>
-      <c r="V10" s="24"/>
-      <c r="W10" s="25"/>
-      <c r="X10" s="23"/>
-      <c r="Y10" s="24"/>
-      <c r="Z10" s="25"/>
-    </row>
-    <row r="11" spans="2:26" ht="24" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="93"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="57" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="29" t="s">
+      <c r="B10" s="100"/>
+      <c r="C10" s="45">
+        <v>1</v>
+      </c>
+      <c r="D10" s="67">
         <v>38</v>
       </c>
-      <c r="G11" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="I11" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="J11" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="K11" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="L11" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="M11" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="N11" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="O11" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="P11" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q11" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="R11" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="S11" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="T11" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="U11" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="V11" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="W11" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="X11" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y11" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z11" s="31" t="s">
-        <v>38</v>
-      </c>
+      <c r="E10" s="58" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="34"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="36"/>
+      <c r="L10" s="34"/>
+      <c r="M10" s="35"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="34"/>
+      <c r="P10" s="35"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="37"/>
+      <c r="S10" s="35"/>
+      <c r="T10" s="36"/>
+      <c r="U10" s="37"/>
+      <c r="V10" s="35"/>
+      <c r="W10" s="36"/>
+      <c r="X10" s="37"/>
+      <c r="Y10" s="35"/>
+      <c r="Z10" s="36"/>
+    </row>
+    <row r="11" spans="2:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="64"/>
+      <c r="C11" s="68">
+        <v>1</v>
+      </c>
+      <c r="D11" s="73"/>
+      <c r="E11" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="23"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="34"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="34"/>
+      <c r="P11" s="35"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="37"/>
+      <c r="S11" s="35"/>
+      <c r="T11" s="36"/>
+      <c r="U11" s="37"/>
+      <c r="V11" s="35"/>
+      <c r="W11" s="36"/>
+      <c r="X11" s="37"/>
+      <c r="Y11" s="35"/>
+      <c r="Z11" s="36"/>
     </row>
     <row r="12" spans="2:26" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="93"/>
-      <c r="C12" s="45">
+      <c r="B12" s="64"/>
+      <c r="C12" s="69">
         <v>1</v>
       </c>
-      <c r="D12" s="67">
-        <v>38</v>
-      </c>
-      <c r="E12" s="58" t="s">
-        <v>68</v>
+      <c r="D12" s="74"/>
+      <c r="E12" s="66" t="s">
+        <v>62</v>
       </c>
       <c r="F12" s="34"/>
       <c r="G12" s="30"/>
@@ -3048,17 +3002,17 @@
       <c r="Y12" s="35"/>
       <c r="Z12" s="36"/>
     </row>
-    <row r="13" spans="2:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:26" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="64"/>
-      <c r="C13" s="68">
+      <c r="C13" s="70">
         <v>1</v>
       </c>
-      <c r="D13" s="73"/>
-      <c r="E13" s="59" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="23"/>
-      <c r="G13" s="4"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="34"/>
+      <c r="G13" s="30"/>
       <c r="H13" s="36"/>
       <c r="I13" s="34"/>
       <c r="J13" s="35"/>
@@ -3081,12 +3035,12 @@
     </row>
     <row r="14" spans="2:26" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="64"/>
-      <c r="C14" s="69">
+      <c r="C14" s="70">
         <v>1</v>
       </c>
-      <c r="D14" s="74"/>
+      <c r="D14" s="75"/>
       <c r="E14" s="66" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F14" s="34"/>
       <c r="G14" s="30"/>
@@ -3116,8 +3070,8 @@
         <v>1</v>
       </c>
       <c r="D15" s="75"/>
-      <c r="E15" s="66" t="s">
-        <v>46</v>
+      <c r="E15" s="65" t="s">
+        <v>64</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="30"/>
@@ -3141,136 +3095,136 @@
       <c r="Y15" s="35"/>
       <c r="Z15" s="36"/>
     </row>
-    <row r="16" spans="2:26" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="64"/>
-      <c r="C16" s="70">
+    <row r="16" spans="2:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="78" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="68">
         <v>1</v>
       </c>
-      <c r="D16" s="75"/>
-      <c r="E16" s="66" t="s">
-        <v>63</v>
-      </c>
-      <c r="F16" s="34"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="36"/>
-      <c r="L16" s="34"/>
-      <c r="M16" s="35"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="34"/>
-      <c r="P16" s="35"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="37"/>
-      <c r="S16" s="35"/>
-      <c r="T16" s="36"/>
-      <c r="U16" s="37"/>
-      <c r="V16" s="35"/>
-      <c r="W16" s="36"/>
-      <c r="X16" s="37"/>
-      <c r="Y16" s="35"/>
-      <c r="Z16" s="36"/>
-    </row>
-    <row r="17" spans="2:26" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="64"/>
-      <c r="C17" s="70">
-        <v>1</v>
-      </c>
-      <c r="D17" s="75"/>
-      <c r="E17" s="65" t="s">
-        <v>64</v>
-      </c>
-      <c r="F17" s="34"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="35"/>
-      <c r="K17" s="36"/>
-      <c r="L17" s="34"/>
-      <c r="M17" s="35"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="34"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="37"/>
-      <c r="S17" s="35"/>
-      <c r="T17" s="36"/>
-      <c r="U17" s="37"/>
-      <c r="V17" s="35"/>
-      <c r="W17" s="36"/>
-      <c r="X17" s="37"/>
-      <c r="Y17" s="35"/>
-      <c r="Z17" s="36"/>
-    </row>
-    <row r="18" spans="2:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="107" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="68">
-        <v>1</v>
-      </c>
+      <c r="D16" s="73"/>
+      <c r="E16" s="59" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="23"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="24"/>
+      <c r="T16" s="25"/>
+      <c r="U16" s="23"/>
+      <c r="V16" s="24"/>
+      <c r="W16" s="25"/>
+      <c r="X16" s="23"/>
+      <c r="Y16" s="24"/>
+      <c r="Z16" s="25"/>
+    </row>
+    <row r="17" spans="2:26" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="79"/>
+      <c r="C17" s="71"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="60" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17" s="6"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="23"/>
+      <c r="V17" s="24"/>
+      <c r="W17" s="25"/>
+      <c r="X17" s="6"/>
+      <c r="Y17" s="4"/>
+      <c r="Z17" s="7"/>
+    </row>
+    <row r="18" spans="2:26" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="79"/>
+      <c r="C18" s="71"/>
       <c r="D18" s="73"/>
-      <c r="E18" s="59" t="s">
-        <v>44</v>
-      </c>
-      <c r="F18" s="23"/>
+      <c r="E18" s="60" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" s="6"/>
       <c r="G18" s="4"/>
-      <c r="H18" s="25"/>
+      <c r="H18" s="7"/>
       <c r="I18" s="23"/>
       <c r="J18" s="24"/>
       <c r="K18" s="25"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="24"/>
-      <c r="N18" s="25"/>
-      <c r="O18" s="26"/>
-      <c r="P18" s="27"/>
-      <c r="Q18" s="28"/>
-      <c r="R18" s="23"/>
-      <c r="S18" s="24"/>
-      <c r="T18" s="25"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="6"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="7"/>
       <c r="U18" s="23"/>
       <c r="V18" s="24"/>
       <c r="W18" s="25"/>
-      <c r="X18" s="23"/>
-      <c r="Y18" s="24"/>
-      <c r="Z18" s="25"/>
-    </row>
-    <row r="19" spans="2:26" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="94"/>
-      <c r="C19" s="71"/>
+      <c r="X18" s="6"/>
+      <c r="Y18" s="4"/>
+      <c r="Z18" s="7"/>
+    </row>
+    <row r="19" spans="2:26" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="79"/>
+      <c r="C19" s="71">
+        <v>1</v>
+      </c>
       <c r="D19" s="73"/>
       <c r="E19" s="60" t="s">
-        <v>45</v>
-      </c>
-      <c r="F19" s="6"/>
+        <v>47</v>
+      </c>
+      <c r="F19" s="23"/>
       <c r="G19" s="4"/>
-      <c r="H19" s="7"/>
+      <c r="H19" s="25"/>
       <c r="I19" s="23"/>
       <c r="J19" s="24"/>
       <c r="K19" s="25"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="6"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="7"/>
+      <c r="L19" s="23"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="25"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="27"/>
+      <c r="Q19" s="28"/>
+      <c r="R19" s="23"/>
+      <c r="S19" s="24"/>
+      <c r="T19" s="25"/>
       <c r="U19" s="23"/>
       <c r="V19" s="24"/>
       <c r="W19" s="25"/>
-      <c r="X19" s="6"/>
-      <c r="Y19" s="4"/>
+      <c r="X19" s="23"/>
+      <c r="Y19" s="24"/>
       <c r="Z19" s="7"/>
     </row>
-    <row r="20" spans="2:26" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="94"/>
-      <c r="C20" s="71"/>
+    <row r="20" spans="2:26" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="79"/>
+      <c r="C20" s="72">
+        <v>1</v>
+      </c>
       <c r="D20" s="73"/>
-      <c r="E20" s="60" t="s">
-        <v>46</v>
+      <c r="E20" s="61" t="s">
+        <v>70</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="4"/>
@@ -3278,30 +3232,30 @@
       <c r="I20" s="23"/>
       <c r="J20" s="24"/>
       <c r="K20" s="25"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="7"/>
+      <c r="L20" s="23"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="25"/>
       <c r="O20" s="9"/>
       <c r="P20" s="8"/>
       <c r="Q20" s="10"/>
       <c r="R20" s="6"/>
       <c r="S20" s="4"/>
       <c r="T20" s="7"/>
-      <c r="U20" s="23"/>
-      <c r="V20" s="24"/>
-      <c r="W20" s="25"/>
+      <c r="U20" s="6"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="7"/>
       <c r="X20" s="6"/>
       <c r="Y20" s="4"/>
       <c r="Z20" s="7"/>
     </row>
-    <row r="21" spans="2:26" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B21" s="94"/>
+    <row r="21" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="79"/>
       <c r="C21" s="71">
         <v>1</v>
       </c>
       <c r="D21" s="73"/>
-      <c r="E21" s="60" t="s">
-        <v>47</v>
+      <c r="E21" s="62" t="s">
+        <v>49</v>
       </c>
       <c r="F21" s="23"/>
       <c r="G21" s="4"/>
@@ -3323,47 +3277,47 @@
       <c r="W21" s="25"/>
       <c r="X21" s="23"/>
       <c r="Y21" s="24"/>
-      <c r="Z21" s="7"/>
-    </row>
-    <row r="22" spans="2:26" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B22" s="94"/>
-      <c r="C22" s="72">
+      <c r="Z21" s="25"/>
+    </row>
+    <row r="22" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="79"/>
+      <c r="C22" s="71">
         <v>1</v>
       </c>
       <c r="D22" s="73"/>
-      <c r="E22" s="61" t="s">
-        <v>70</v>
-      </c>
-      <c r="F22" s="6"/>
+      <c r="E22" s="62" t="s">
+        <v>50</v>
+      </c>
+      <c r="F22" s="23"/>
       <c r="G22" s="4"/>
-      <c r="H22" s="7"/>
+      <c r="H22" s="25"/>
       <c r="I22" s="23"/>
       <c r="J22" s="24"/>
       <c r="K22" s="25"/>
       <c r="L22" s="23"/>
       <c r="M22" s="24"/>
       <c r="N22" s="25"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="8"/>
-      <c r="Q22" s="10"/>
-      <c r="R22" s="6"/>
-      <c r="S22" s="4"/>
-      <c r="T22" s="7"/>
-      <c r="U22" s="6"/>
-      <c r="V22" s="4"/>
-      <c r="W22" s="7"/>
-      <c r="X22" s="6"/>
-      <c r="Y22" s="4"/>
-      <c r="Z22" s="7"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="27"/>
+      <c r="Q22" s="28"/>
+      <c r="R22" s="23"/>
+      <c r="S22" s="24"/>
+      <c r="T22" s="25"/>
+      <c r="U22" s="23"/>
+      <c r="V22" s="24"/>
+      <c r="W22" s="25"/>
+      <c r="X22" s="23"/>
+      <c r="Y22" s="24"/>
+      <c r="Z22" s="25"/>
     </row>
     <row r="23" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="94"/>
+      <c r="B23" s="79"/>
       <c r="C23" s="71">
         <v>1</v>
       </c>
       <c r="D23" s="73"/>
       <c r="E23" s="62" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F23" s="23"/>
       <c r="G23" s="4"/>
@@ -3387,78 +3341,47 @@
       <c r="Y23" s="24"/>
       <c r="Z23" s="25"/>
     </row>
-    <row r="24" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="94"/>
-      <c r="C24" s="71">
-        <v>1</v>
-      </c>
-      <c r="D24" s="73"/>
-      <c r="E24" s="62" t="s">
-        <v>50</v>
-      </c>
-      <c r="F24" s="23"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="25"/>
-      <c r="L24" s="23"/>
-      <c r="M24" s="24"/>
-      <c r="N24" s="25"/>
-      <c r="O24" s="26"/>
-      <c r="P24" s="27"/>
-      <c r="Q24" s="28"/>
-      <c r="R24" s="23"/>
-      <c r="S24" s="24"/>
-      <c r="T24" s="25"/>
-      <c r="U24" s="23"/>
-      <c r="V24" s="24"/>
-      <c r="W24" s="25"/>
-      <c r="X24" s="23"/>
-      <c r="Y24" s="24"/>
-      <c r="Z24" s="25"/>
-    </row>
-    <row r="25" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="94"/>
-      <c r="C25" s="71">
-        <v>1</v>
-      </c>
-      <c r="D25" s="73"/>
-      <c r="E25" s="62" t="s">
-        <v>51</v>
-      </c>
-      <c r="F25" s="23"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="25"/>
-      <c r="L25" s="23"/>
-      <c r="M25" s="24"/>
-      <c r="N25" s="25"/>
-      <c r="O25" s="26"/>
-      <c r="P25" s="27"/>
-      <c r="Q25" s="28"/>
-      <c r="R25" s="23"/>
-      <c r="S25" s="24"/>
-      <c r="T25" s="25"/>
-      <c r="U25" s="23"/>
-      <c r="V25" s="24"/>
-      <c r="W25" s="25"/>
-      <c r="X25" s="23"/>
-      <c r="Y25" s="24"/>
-      <c r="Z25" s="25"/>
+    <row r="24" spans="2:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="49"/>
+      <c r="C24" s="101" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="102"/>
+      <c r="E24" s="103"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="47" t="s">
+        <v>55</v>
+      </c>
+      <c r="O24" s="50"/>
+      <c r="P24" s="50"/>
+      <c r="Q24" s="50"/>
+      <c r="Z24" s="51"/>
+    </row>
+    <row r="25" spans="2:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="49"/>
+      <c r="C25" s="101" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="102"/>
+      <c r="E25" s="103"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="47" t="s">
+        <v>55</v>
+      </c>
+      <c r="O25" s="50"/>
+      <c r="P25" s="50"/>
+      <c r="Q25" s="50"/>
+      <c r="Z25" s="51"/>
     </row>
     <row r="26" spans="2:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="49"/>
-      <c r="C26" s="78" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="79"/>
-      <c r="E26" s="80"/>
-      <c r="F26" s="38"/>
+      <c r="C26" s="101" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="102"/>
+      <c r="E26" s="103"/>
       <c r="G26" s="47" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O26" s="50"/>
       <c r="P26" s="50"/>
@@ -3467,104 +3390,73 @@
     </row>
     <row r="27" spans="2:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="49"/>
-      <c r="C27" s="78" t="s">
-        <v>54</v>
-      </c>
-      <c r="D27" s="79"/>
-      <c r="E27" s="80"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="47" t="s">
-        <v>55</v>
-      </c>
+      <c r="C27" s="104" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="104"/>
+      <c r="E27" s="63" t="s">
+        <v>65</v>
+      </c>
+      <c r="G27" s="54"/>
       <c r="O27" s="50"/>
       <c r="P27" s="50"/>
       <c r="Q27" s="50"/>
       <c r="Z27" s="51"/>
     </row>
-    <row r="28" spans="2:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="49"/>
-      <c r="C28" s="78" t="s">
-        <v>56</v>
-      </c>
-      <c r="D28" s="79"/>
-      <c r="E28" s="80"/>
-      <c r="G28" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="O28" s="50"/>
-      <c r="P28" s="50"/>
-      <c r="Q28" s="50"/>
-      <c r="Z28" s="51"/>
-    </row>
-    <row r="29" spans="2:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="49"/>
-      <c r="C29" s="81" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" s="81"/>
-      <c r="E29" s="63" t="s">
-        <v>65</v>
-      </c>
-      <c r="G29" s="54"/>
-      <c r="O29" s="50"/>
-      <c r="P29" s="50"/>
-      <c r="Q29" s="50"/>
-      <c r="Z29" s="51"/>
-    </row>
-    <row r="30" spans="2:26" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="82" t="s">
+    <row r="28" spans="2:26" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="83"/>
-      <c r="D30" s="83"/>
-      <c r="E30" s="84" t="s">
+      <c r="C28" s="106"/>
+      <c r="D28" s="106"/>
+      <c r="E28" s="107" t="s">
         <v>66</v>
       </c>
-      <c r="F30" s="84"/>
-      <c r="G30" s="84"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="39"/>
-      <c r="J30" s="39"/>
-      <c r="K30" s="39"/>
-      <c r="L30" s="39"/>
-      <c r="M30" s="39"/>
-      <c r="N30" s="39"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="39"/>
-      <c r="Q30" s="39"/>
-      <c r="R30" s="39"/>
-      <c r="S30" s="39"/>
-      <c r="T30" s="39"/>
-      <c r="U30" s="39"/>
-      <c r="V30" s="39"/>
-      <c r="W30" s="39"/>
-      <c r="X30" s="39"/>
-      <c r="Y30" s="39"/>
-      <c r="Z30" s="40"/>
-    </row>
-    <row r="31" spans="2:26" ht="21" x14ac:dyDescent="0.25">
-      <c r="B31" s="52"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="53"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="F28" s="107"/>
+      <c r="G28" s="107"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="39"/>
+      <c r="K28" s="39"/>
+      <c r="L28" s="39"/>
+      <c r="M28" s="39"/>
+      <c r="N28" s="39"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="39"/>
+      <c r="Q28" s="39"/>
+      <c r="R28" s="39"/>
+      <c r="S28" s="39"/>
+      <c r="T28" s="39"/>
+      <c r="U28" s="39"/>
+      <c r="V28" s="39"/>
+      <c r="W28" s="39"/>
+      <c r="X28" s="39"/>
+      <c r="Y28" s="39"/>
+      <c r="Z28" s="40"/>
+    </row>
+    <row r="29" spans="2:26" ht="21" x14ac:dyDescent="0.25">
+      <c r="B29" s="52"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="53"/>
+    </row>
+    <row r="31" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0"/>
   <mergeCells count="20">
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
     <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:G28"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
     <mergeCell ref="U4:W4"/>
     <mergeCell ref="X4:Z4"/>
-    <mergeCell ref="B6:B12"/>
-    <mergeCell ref="B18:B25"/>
+    <mergeCell ref="B6:B10"/>
+    <mergeCell ref="B16:B23"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
@@ -3580,18 +3472,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3a415345-6a39-4751-b960-4fc8f12baef7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="74ad866f-79dd-4f7a-ba3c-81e3e663768c" xsi:nil="true"/>
-    <MediaLengthInSeconds xmlns="3a415345-6a39-4751-b960-4fc8f12baef7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3600,7 +3480,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101005C25850FC8DE9B4F9FFF86415CB592F7" ma:contentTypeVersion="16" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="e2d06f0efc13322f1d89eb588b0b5b4f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3a415345-6a39-4751-b960-4fc8f12baef7" xmlns:ns3="74ad866f-79dd-4f7a-ba3c-81e3e663768c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49ef3c2ba543efacb40b65122bf2570d" ns2:_="" ns3:_="">
     <xsd:import namespace="3a415345-6a39-4751-b960-4fc8f12baef7"/>
@@ -3841,18 +3721,19 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6192A4F-43EB-47CE-AABA-403827665463}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3a415345-6a39-4751-b960-4fc8f12baef7"/>
-    <ds:schemaRef ds:uri="74ad866f-79dd-4f7a-ba3c-81e3e663768c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3a415345-6a39-4751-b960-4fc8f12baef7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="74ad866f-79dd-4f7a-ba3c-81e3e663768c" xsi:nil="true"/>
+    <MediaLengthInSeconds xmlns="3a415345-6a39-4751-b960-4fc8f12baef7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A9F4E51-4DE3-4214-9644-9D529D38719F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -3860,7 +3741,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6636811-7CA6-4FDB-96A2-751F968F6359}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3877,4 +3758,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6192A4F-43EB-47CE-AABA-403827665463}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3a415345-6a39-4751-b960-4fc8f12baef7"/>
+    <ds:schemaRef ds:uri="74ad866f-79dd-4f7a-ba3c-81e3e663768c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>